--- a/simulations/lab3/measured/Lab3-數據記錄.xlsx
+++ b/simulations/lab3/measured/Lab3-數據記錄.xlsx
@@ -146,12 +146,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -297,12 +298,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$C$6:$C$10</f>
+              <f>'實驗一 特性曲線'!$C$8:$C$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -328,12 +329,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$D$6:$D$10</f>
+              <f>'實驗一 特性曲線'!$F$8:$F$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -367,12 +368,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$F$6:$F$10</f>
+              <f>'實驗一 特性曲線'!$H$8:$H$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -398,12 +399,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$G$6:$G$10</f>
+              <f>'實驗一 特性曲線'!$K$8:$K$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -437,12 +438,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$I$6:$I$10</f>
+              <f>'實驗一 特性曲線'!$M$8:$M$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -468,12 +469,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$J$6:$J$10</f>
+              <f>'實驗一 特性曲線'!$P$8:$P$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -507,12 +508,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$L$6:$L$10</f>
+              <f>'實驗一 特性曲線'!$R$8:$R$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -538,12 +539,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$A$6:$A$10</f>
+              <f>'實驗一 特性曲線'!$A$8:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$M$6:$M$10</f>
+              <f>'實驗一 特性曲線'!$U$8:$U$12</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -663,12 +664,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$C$6:$C$11</f>
+              <f>'實驗二 轉移曲線'!$D$8:$D$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -694,12 +695,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$D$6:$D$11</f>
+              <f>'實驗二 轉移曲線'!$E$8:$E$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -733,12 +734,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$F$6:$F$11</f>
+              <f>'實驗二 轉移曲線'!$H$8:$H$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -764,12 +765,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$G$6:$G$11</f>
+              <f>'實驗二 轉移曲線'!$I$8:$I$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -803,12 +804,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$I$6:$I$11</f>
+              <f>'實驗二 轉移曲線'!$L$8:$L$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -834,12 +835,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$6:$A$11</f>
+              <f>'實驗二 轉移曲線'!$A$8:$A$13</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$J$6:$J$11</f>
+              <f>'實驗二 轉移曲線'!$M$8:$M$13</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -959,12 +960,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$A$15:$A$24</f>
+              <f>'實驗二 轉移曲線'!$A$20:$A$29</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗二 轉移曲線'!$D$15:$D$24</f>
+              <f>'實驗二 轉移曲線'!$D$20:$D$29</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1040,7 +1041,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -1067,7 +1068,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -1089,7 +1090,7 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
@@ -1563,22 +1564,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1596,309 +1605,546 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>V_GS = 0 V</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>V_GS = 2 V</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>V_GS = 4 V</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>V_GS = 6 V</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>源極取樣電阻 R1 (Ω)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>← 講義指定 1 kΩ；改這一格，所有 I_D 與元件電壓欄會跟著變</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>V_GS 設定 = 0 V</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>V_GS 設定 = 2 V</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>V_GS 設定 = 4 V</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>V_GS 設定 = 6 V</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>V_DS 設定 (V)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>V_R1 量測 (V)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>V_R1 量測 (V)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>V_R1 量測 (V)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>V_R1 量測 (V)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>I_D = V_R1/R1 (mA)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>V_GS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>V_DS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice I_D (mA)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>I_D = V_R1/R1 (mA)</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>V_GS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>V_DS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice I_D (mA)</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>I_D = V_R1/R1 (mA)</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>V_GS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>V_DS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice I_D (mA)</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>I_D = V_R1/R1 (mA)</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>V_GS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>V_DS 元件 (V)</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice I_D (mA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="10">
-        <f>IF(B6="","",B6/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="11">
+        <f>IF(B8="","",B8/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>IF(B8="","",0.0-B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>IF(B8="","",$A8-B8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="10">
-        <f>IF(E6="","",E6/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="11">
+        <f>IF(G8="","",G8/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="I8" s="11">
+        <f>IF(G8="","",2.0-G8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="11">
+        <f>IF(G8="","",$A8-G8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12" t="n">
         <v>0.0153</v>
       </c>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="10">
-        <f>IF(H6="","",H6/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="n">
+      <c r="L8" s="10" t="inlineStr"/>
+      <c r="M8" s="11">
+        <f>IF(L8="","",L8/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="N8" s="11">
+        <f>IF(L8="","",4.0-L8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="11">
+        <f>IF(L8="","",$A8-L8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="12" t="n">
         <v>0.9858</v>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="10">
-        <f>IF(K6="","",K6/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="M6" s="11" t="n">
+      <c r="Q8" s="10" t="inlineStr"/>
+      <c r="R8" s="11">
+        <f>IF(Q8="","",Q8/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="S8" s="11">
+        <f>IF(Q8="","",6.0-Q8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="11">
+        <f>IF(Q8="","",$A8-Q8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="12" t="n">
         <v>0.9957</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+    <row r="9">
+      <c r="A9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10">
-        <f>IF(B7="","",B7/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="11">
+        <f>IF(B9="","",B9/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>IF(B9="","",0.0-B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>IF(B9="","",$A9-B9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="10">
-        <f>IF(E7="","",E7/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G7" s="11" t="n">
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="11">
+        <f>IF(G9="","",G9/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="I9" s="11">
+        <f>IF(G9="","",2.0-G9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="11">
+        <f>IF(G9="","",$A9-G9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>0.0158</v>
       </c>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="10">
-        <f>IF(H7="","",H7/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="n">
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="11">
+        <f>IF(L9="","",L9/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="N9" s="11">
+        <f>IF(L9="","",4.0-L9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="11">
+        <f>IF(L9="","",$A9-L9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="12" t="n">
         <v>1.6567</v>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="10">
-        <f>IF(K7="","",K7/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="M7" s="11" t="n">
+      <c r="Q9" s="10" t="inlineStr"/>
+      <c r="R9" s="11">
+        <f>IF(Q9="","",Q9/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="S9" s="11">
+        <f>IF(Q9="","",6.0-Q9)</f>
+        <v/>
+      </c>
+      <c r="T9" s="11">
+        <f>IF(Q9="","",$A9-Q9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="12" t="n">
         <v>1.9867</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
+    <row r="10">
+      <c r="A10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="10">
-        <f>IF(B8="","",B8/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="11">
+        <f>IF(B10="","",B10/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>IF(B10="","",0.0-B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>IF(B10="","",$A10-B10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="10">
-        <f>IF(E8="","",E8/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G8" s="11" t="n">
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="11">
+        <f>IF(G10="","",G10/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>IF(G10="","",2.0-G10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="11">
+        <f>IF(G10="","",$A10-G10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12" t="n">
         <v>0.0162</v>
       </c>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="10">
-        <f>IF(H8="","",H8/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="n">
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="11">
+        <f>IF(L10="","",L10/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="N10" s="11">
+        <f>IF(L10="","",4.0-L10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="11">
+        <f>IF(L10="","",$A10-L10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="12" t="n">
         <v>1.6621</v>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="10">
-        <f>IF(K8="","",K8/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="M8" s="11" t="n">
+      <c r="Q10" s="10" t="inlineStr"/>
+      <c r="R10" s="11">
+        <f>IF(Q10="","",Q10/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="S10" s="11">
+        <f>IF(Q10="","",6.0-Q10)</f>
+        <v/>
+      </c>
+      <c r="T10" s="11">
+        <f>IF(Q10="","",$A10-Q10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="12" t="n">
         <v>2.958</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+    <row r="11">
+      <c r="A11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="10">
-        <f>IF(B9="","",B9/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="B11" s="10" t="inlineStr"/>
+      <c r="C11" s="11">
+        <f>IF(B11="","",B11/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>IF(B11="","",0.0-B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>IF(B11="","",$A11-B11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="10">
-        <f>IF(E9="","",E9/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="11">
+        <f>IF(G11="","",G11/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="I11" s="11">
+        <f>IF(G11="","",2.0-G11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="11">
+        <f>IF(G11="","",$A11-G11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>0.0165</v>
       </c>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="10">
-        <f>IF(H9="","",H9/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="n">
+      <c r="L11" s="10" t="inlineStr"/>
+      <c r="M11" s="11">
+        <f>IF(L11="","",L11/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="N11" s="11">
+        <f>IF(L11="","",4.0-L11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="11">
+        <f>IF(L11="","",$A11-L11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="12" t="n">
         <v>1.6654</v>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="10">
-        <f>IF(K9="","",K9/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="M9" s="11" t="n">
+      <c r="Q11" s="10" t="inlineStr"/>
+      <c r="R11" s="11">
+        <f>IF(Q11="","",Q11/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="S11" s="11">
+        <f>IF(Q11="","",6.0-Q11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="11">
+        <f>IF(Q11="","",$A11-Q11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="12" t="n">
         <v>3.5621</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
+    <row r="12">
+      <c r="A12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="10">
-        <f>IF(B10="","",B10/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11" t="n">
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="11">
+        <f>IF(B12="","",B12/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>IF(B12="","",0.0-B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>IF(B12="","",$A12-B12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="10">
-        <f>IF(E10="","",E10/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G10" s="11" t="n">
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="11">
+        <f>IF(G12="","",G12/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="I12" s="11">
+        <f>IF(G12="","",2.0-G12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="11">
+        <f>IF(G12="","",$A12-G12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>0.0168</v>
       </c>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="10">
-        <f>IF(H10="","",H10/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="n">
+      <c r="L12" s="10" t="inlineStr"/>
+      <c r="M12" s="11">
+        <f>IF(L12="","",L12/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="N12" s="11">
+        <f>IF(L12="","",4.0-L12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="11">
+        <f>IF(L12="","",$A12-L12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="12" t="n">
         <v>1.668</v>
       </c>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="10">
-        <f>IF(K10="","",K10/1000.0*1000)</f>
-        <v/>
-      </c>
-      <c r="M10" s="11" t="n">
+      <c r="Q12" s="10" t="inlineStr"/>
+      <c r="R12" s="11">
+        <f>IF(Q12="","",Q12/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="S12" s="11">
+        <f>IF(Q12="","",6.0-Q12)</f>
+        <v/>
+      </c>
+      <c r="T12" s="11">
+        <f>IF(Q12="","",$A12-Q12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="12" t="n">
         <v>3.5701</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>助教只要求至少一條導通的（V_GS = 2／4／6 V 擇一以上）；V_GS = 0 V 那組建議還是量一次，當作「截止區電流為零」的證據。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>V_GS = 6 V 在低 V_DS 時每加 1 V 電流約多 1 mA，那是 1 kΩ 的斜率、不是元件的三極管電阻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>只要量 R1 的壓降這一個電壓就夠：汲極直接接在 CH2 上，V_D 必定等於電源設定值，所以元件真正的 V_GS 與 V_DS 都可以由 V_R1 減出來（右邊兩欄已自動算好）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>報告要畫「元件端」的特性曲線時，橫軸用 V_DS 元件 那一欄，不是最左邊的電源設定值。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="L6:P6"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="Q6:U6"/>
+    <mergeCell ref="G6:K6"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1912,7 +2158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1920,11 +2166,14 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1942,497 +2191,562 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>V_DS = 1 V</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>V_DS = 3 V</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>V_DS = 5 V</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>汲極取樣電阻 R1 (Ω)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>← 講義指定 100 Ω；改這一格，所有 I_D 換算欄會跟著變</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>V_DS 設定 = 1 V</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>V_DS 設定 = 3 V</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>V_DS 設定 = 5 V</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>V_GS 設定 (V)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_D (V)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>I_D (mA)</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice (mA)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_D (V)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>I_D (mA)</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice (mA)</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_D (V)</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>實測 V_R1 (V)</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>I_D (mA)</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>LTspice (mA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="11">
+        <f>IF(C8&lt;&gt;"",C8/$B$4*1000,IF(B8&lt;&gt;"",(1.0-B8)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="11">
+        <f>IF(G8&lt;&gt;"",G8/$B$4*1000,IF(F8&lt;&gt;"",(3.0-F8)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr"/>
+      <c r="L8" s="11">
+        <f>IF(K8&lt;&gt;"",K8/$B$4*1000,IF(J8&lt;&gt;"",(5.0-J8)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="11">
+        <f>IF(C9&lt;&gt;"",C9/$B$4*1000,IF(B9&lt;&gt;"",(1.0-B9)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="11">
+        <f>IF(G9&lt;&gt;"",G9/$B$4*1000,IF(F9&lt;&gt;"",(3.0-F9)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
+      <c r="L9" s="11">
+        <f>IF(K9&lt;&gt;"",K9/$B$4*1000,IF(J9&lt;&gt;"",(5.0-J9)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="11">
+        <f>IF(C10&lt;&gt;"",C10/$B$4*1000,IF(B10&lt;&gt;"",(1.0-B10)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="11">
+        <f>IF(G10&lt;&gt;"",G10/$B$4*1000,IF(F10&lt;&gt;"",(3.0-F10)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="11">
+        <f>IF(K10&lt;&gt;"",K10/$B$4*1000,IF(J10&lt;&gt;"",(5.0-J10)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>0.0207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="11">
+        <f>IF(C11&lt;&gt;"",C11/$B$4*1000,IF(B11&lt;&gt;"",(1.0-B11)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>8.633100000000001</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="11">
+        <f>IF(G11&lt;&gt;"",G11/$B$4*1000,IF(F11&lt;&gt;"",(3.0-F11)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>24.7749</v>
+      </c>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr"/>
+      <c r="L11" s="11">
+        <f>IF(K11&lt;&gt;"",K11/$B$4*1000,IF(J11&lt;&gt;"",(5.0-J11)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>31.346</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="11">
+        <f>IF(C12&lt;&gt;"",C12/$B$4*1000,IF(B12&lt;&gt;"",(1.0-B12)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>9.3596</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="11">
+        <f>IF(G12&lt;&gt;"",G12/$B$4*1000,IF(F12&lt;&gt;"",(3.0-F12)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>28.0076</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr"/>
+      <c r="L12" s="11">
+        <f>IF(K12&lt;&gt;"",K12/$B$4*1000,IF(J12&lt;&gt;"",(5.0-J12)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>46.5403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="11">
+        <f>IF(C13&lt;&gt;"",C13/$B$4*1000,IF(B13&lt;&gt;"",(1.0-B13)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>9.578200000000001</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="11">
+        <f>IF(G13&lt;&gt;"",G13/$B$4*1000,IF(F13&lt;&gt;"",(3.0-F13)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>28.7152</v>
+      </c>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="11">
+        <f>IF(K13&lt;&gt;"",K13/$B$4*1000,IF(J13&lt;&gt;"",(5.0-J13)/$B$4*1000,""))</f>
+        <v/>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>47.8244</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>兩欄電壓量其中一個就夠，兩個都量是為了當場對帳：V_D + V_R1 應該等於該組的 V_DS 設定值，對不起來就是有一次量錯。I_D 欄優先用 V_R1，沒填時自動改用 (V_DS − V_D)/R1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>源極已接地，所以 V_D 就是元件真正的 V_DS、電源設定的 V_GS 就是元件真正的 V_GS，不用再減。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>加密掃描（找 V_th 用）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>選用的 V_DS (V) →</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>V_GS 設定 (V)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>V_D 量測 (V)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>I_D (mA)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>V_D 量測 (V)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>√I_D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11">
+        <f>IF(OR(A20="",B20="",$D$18=""),"",($D$18-B20)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>IF(C20="","",SQRT(C20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="11">
+        <f>IF(OR(A21="",B21="",$D$18=""),"",($D$18-B21)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>IF(C21="","",SQRT(C21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="11">
+        <f>IF(OR(A22="",B22="",$D$18=""),"",($D$18-B22)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>IF(C22="","",SQRT(C22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr"/>
+      <c r="C23" s="11">
+        <f>IF(OR(A23="",B23="",$D$18=""),"",($D$18-B23)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>IF(C23="","",SQRT(C23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr"/>
+      <c r="B24" s="10" t="inlineStr"/>
+      <c r="C24" s="11">
+        <f>IF(OR(A24="",B24="",$D$18=""),"",($D$18-B24)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>IF(C24="","",SQRT(C24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr"/>
+      <c r="B25" s="10" t="inlineStr"/>
+      <c r="C25" s="11">
+        <f>IF(OR(A25="",B25="",$D$18=""),"",($D$18-B25)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>IF(C25="","",SQRT(C25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr"/>
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="11">
+        <f>IF(OR(A26="",B26="",$D$18=""),"",($D$18-B26)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>IF(C26="","",SQRT(C26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="11">
+        <f>IF(OR(A27="",B27="",$D$18=""),"",($D$18-B27)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>IF(C27="","",SQRT(C27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr"/>
+      <c r="B28" s="10" t="inlineStr"/>
+      <c r="C28" s="11">
+        <f>IF(OR(A28="",B28="",$D$18=""),"",($D$18-B28)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>IF(C28="","",SQRT(C28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="11">
+        <f>IF(OR(A29="",B29="",$D$18=""),"",($D$18-B29)/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>IF(C29="","",SQRT(C29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>做法：先看粗掃表在哪一格之間跳起來，回到那一段用 0.1～0.2 V 一階重掃十點；√I_D 欄若呈一條直線就代表那幾點在平方律上，可以拿來外插。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>臨界電壓 V_th（平方根外插）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>量測點 1</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>量測點 2</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>外插結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>V_GS (V)</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr"/>
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="11">
+        <f>IF(OR(B34="",B35="",C34="",C35=""),"",B34-(C34-B34)/(SQRT(C35)-SQRT(B35))*SQRT(B35))</f>
+        <v/>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>← V_th (V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>I_D (mA)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>V_D 量測 (V)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>LTspice (mA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="10">
-        <f>IF(B6="","",(1.0-B6)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="10">
-        <f>IF(E6="","",(3.0-E6)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="10">
-        <f>IF(H6="","",(5.0-H6)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10">
-        <f>IF(B7="","",(1.0-B7)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="10">
-        <f>IF(E7="","",(3.0-E7)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="10">
-        <f>IF(H7="","",(5.0-H7)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="10">
-        <f>IF(B8="","",(1.0-B8)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="10">
-        <f>IF(E8="","",(3.0-E8)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="10">
-        <f>IF(H8="","",(5.0-H8)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0.0207</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="10">
-        <f>IF(B9="","",(1.0-B9)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>8.633100000000001</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="10">
-        <f>IF(E9="","",(3.0-E9)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>24.7749</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="10">
-        <f>IF(H9="","",(5.0-H9)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>31.346</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="10">
-        <f>IF(B10="","",(1.0-B10)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>9.3596</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="10">
-        <f>IF(E10="","",(3.0-E10)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>28.0076</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="10">
-        <f>IF(H10="","",(5.0-H10)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>46.5403</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="10">
-        <f>IF(B11="","",(1.0-B11)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>9.578200000000001</v>
-      </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="10">
-        <f>IF(E11="","",(3.0-E11)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>28.7152</v>
-      </c>
-      <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="10">
-        <f>IF(H11="","",(5.0-H11)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>47.8244</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>加密掃描（找 V_th 用）</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>選用的 V_DS (V) →</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>V_GS 設定 (V)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>V_D 量測 (V)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>√I_D</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="10">
-        <f>IF(OR(A15="",B15="",$D$13=""),"",($D$13-B15)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D15" s="10">
-        <f>IF(C15="","",SQRT(C15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="10">
-        <f>IF(OR(A16="",B16="",$D$13=""),"",($D$13-B16)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D16" s="10">
-        <f>IF(C16="","",SQRT(C16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr"/>
-      <c r="B17" s="9" t="inlineStr"/>
-      <c r="C17" s="10">
-        <f>IF(OR(A17="",B17="",$D$13=""),"",($D$13-B17)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D17" s="10">
-        <f>IF(C17="","",SQRT(C17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10">
-        <f>IF(OR(A18="",B18="",$D$13=""),"",($D$13-B18)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D18" s="10">
-        <f>IF(C18="","",SQRT(C18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr"/>
-      <c r="B19" s="9" t="inlineStr"/>
-      <c r="C19" s="10">
-        <f>IF(OR(A19="",B19="",$D$13=""),"",($D$13-B19)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D19" s="10">
-        <f>IF(C19="","",SQRT(C19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
-      <c r="B20" s="9" t="inlineStr"/>
-      <c r="C20" s="10">
-        <f>IF(OR(A20="",B20="",$D$13=""),"",($D$13-B20)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D20" s="10">
-        <f>IF(C20="","",SQRT(C20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr"/>
-      <c r="B21" s="9" t="inlineStr"/>
-      <c r="C21" s="10">
-        <f>IF(OR(A21="",B21="",$D$13=""),"",($D$13-B21)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D21" s="10">
-        <f>IF(C21="","",SQRT(C21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr"/>
-      <c r="C22" s="10">
-        <f>IF(OR(A22="",B22="",$D$13=""),"",($D$13-B22)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D22" s="10">
-        <f>IF(C22="","",SQRT(C22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr"/>
-      <c r="C23" s="10">
-        <f>IF(OR(A23="",B23="",$D$13=""),"",($D$13-B23)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D23" s="10">
-        <f>IF(C23="","",SQRT(C23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="10">
-        <f>IF(OR(A24="",B24="",$D$13=""),"",($D$13-B24)/100.0*1000)</f>
-        <v/>
-      </c>
-      <c r="D24" s="10">
-        <f>IF(C24="","",SQRT(C24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>做法：先看粗掃表在哪一格之間跳起來，回到那一段用 0.1～0.2 V 一階重掃十點；√I_D 欄若呈一條直線就代表那幾點在平方律上，可以拿來外插。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>臨界電壓 V_th（平方根外插）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr"/>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>量測點 1</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>量測點 2</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>外插結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>V_GS (V)</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr"/>
-      <c r="C29" s="13" t="inlineStr"/>
-      <c r="D29" s="10">
-        <f>IF(OR(B29="",B30="",C29="",C30=""),"",B29-(C29-B29)/(SQRT(C30)-SQRT(B30))*SQRT(B30))</f>
-        <v/>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>← V_th (V)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>I_D (mA)</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
+      <c r="B35" s="10" t="inlineStr"/>
+      <c r="C35" s="10" t="inlineStr"/>
+      <c r="D35" s="12" t="n">
         <v>2.14</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>← LTspice（BS170）的 V_to</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="D31" s="14">
-        <f>IF(D29="","",IF(OR(D29&lt;0,D29&gt;MIN(B29,C29)),"兩點取在平台上了，重挑","合理"))</f>
-        <v/>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+    <row r="36">
+      <c r="D36" s="15">
+        <f>IF(D34="","",IF(OR(D34&lt;0,D34&gt;MIN(B34,C34)),"兩點取在平台上了，重挑","合理"))</f>
+        <v/>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>← 合理性檢查</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>兩個點都要取自上面的加密掃描、且落在抬頭段（建議 I_D 在 1～5 mA 之間）。取到被 R1 限流的平台（I_D 接近 V_DS/100 Ω）會算出負的 V_th。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>三組的平台高度約等於 V_DS / 100 Ω，那是 R1 在限流、不是元件飽和；要讀的資訊全在抬頭那一段。</t>
         </is>
@@ -2440,10 +2754,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="F6:I6"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2488,274 +2802,274 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>V_GS = 0 V</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="B5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>V_GS = 2 V</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>V_DS (experimental setting)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>V_DS (experimental setting)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="B7" s="15">
-        <f>IF('實驗一 特性曲線'!C6="","",TEXT('實驗一 特性曲線'!C6,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="B7" s="16">
+        <f>IF('實驗一 特性曲線'!C8="","",TEXT('實驗一 特性曲線'!C8,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="E7" s="15">
-        <f>IF('實驗一 特性曲線'!F6="","",TEXT('實驗一 特性曲線'!F6,"0.000")&amp;" mA")</f>
+      <c r="E7" s="16">
+        <f>IF('實驗一 特性曲線'!H8="","",TEXT('實驗一 特性曲線'!H8,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="B8" s="15">
-        <f>IF('實驗一 特性曲線'!C7="","",TEXT('實驗一 特性曲線'!C7,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="B8" s="16">
+        <f>IF('實驗一 特性曲線'!C9="","",TEXT('實驗一 特性曲線'!C9,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="E8" s="15">
-        <f>IF('實驗一 特性曲線'!F7="","",TEXT('實驗一 特性曲線'!F7,"0.000")&amp;" mA")</f>
+      <c r="E8" s="16">
+        <f>IF('實驗一 特性曲線'!H9="","",TEXT('實驗一 特性曲線'!H9,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="B9" s="15">
-        <f>IF('實驗一 特性曲線'!C8="","",TEXT('實驗一 特性曲線'!C8,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="B9" s="16">
+        <f>IF('實驗一 特性曲線'!C10="","",TEXT('實驗一 特性曲線'!C10,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="E9" s="15">
-        <f>IF('實驗一 特性曲線'!F8="","",TEXT('實驗一 特性曲線'!F8,"0.000")&amp;" mA")</f>
+      <c r="E9" s="16">
+        <f>IF('實驗一 特性曲線'!H10="","",TEXT('實驗一 特性曲線'!H10,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="B10" s="15">
-        <f>IF('實驗一 特性曲線'!C9="","",TEXT('實驗一 特性曲線'!C9,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="B10" s="16">
+        <f>IF('實驗一 特性曲線'!C11="","",TEXT('實驗一 特性曲線'!C11,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="E10" s="15">
-        <f>IF('實驗一 特性曲線'!F9="","",TEXT('實驗一 特性曲線'!F9,"0.000")&amp;" mA")</f>
+      <c r="E10" s="16">
+        <f>IF('實驗一 特性曲線'!H11="","",TEXT('實驗一 特性曲線'!H11,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="B11" s="15">
-        <f>IF('實驗一 特性曲線'!C10="","",TEXT('實驗一 特性曲線'!C10,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="B11" s="16">
+        <f>IF('實驗一 特性曲線'!C12="","",TEXT('實驗一 特性曲線'!C12,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="E11" s="15">
-        <f>IF('實驗一 特性曲線'!F10="","",TEXT('實驗一 特性曲線'!F10,"0.000")&amp;" mA")</f>
+      <c r="E11" s="16">
+        <f>IF('實驗一 特性曲線'!H12="","",TEXT('實驗一 特性曲線'!H12,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>V_GS = 4 V</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>V_GS = 6 V</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>V_DS (experimental setting)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>V_DS (experimental setting)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="B15" s="15">
-        <f>IF('實驗一 特性曲線'!I6="","",TEXT('實驗一 特性曲線'!I6,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="B15" s="16">
+        <f>IF('實驗一 特性曲線'!M8="","",TEXT('實驗一 特性曲線'!M8,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="E15" s="15">
-        <f>IF('實驗一 特性曲線'!L6="","",TEXT('實驗一 特性曲線'!L6,"0.000")&amp;" mA")</f>
+      <c r="E15" s="16">
+        <f>IF('實驗一 特性曲線'!R8="","",TEXT('實驗一 特性曲線'!R8,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="B16" s="15">
-        <f>IF('實驗一 特性曲線'!I7="","",TEXT('實驗一 特性曲線'!I7,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="B16" s="16">
+        <f>IF('實驗一 特性曲線'!M9="","",TEXT('實驗一 特性曲線'!M9,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="E16" s="15">
-        <f>IF('實驗一 特性曲線'!L7="","",TEXT('實驗一 特性曲線'!L7,"0.000")&amp;" mA")</f>
+      <c r="E16" s="16">
+        <f>IF('實驗一 特性曲線'!R9="","",TEXT('實驗一 特性曲線'!R9,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="B17" s="15">
-        <f>IF('實驗一 特性曲線'!I8="","",TEXT('實驗一 特性曲線'!I8,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="B17" s="16">
+        <f>IF('實驗一 特性曲線'!M10="","",TEXT('實驗一 特性曲線'!M10,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="E17" s="15">
-        <f>IF('實驗一 特性曲線'!L8="","",TEXT('實驗一 特性曲線'!L8,"0.000")&amp;" mA")</f>
+      <c r="E17" s="16">
+        <f>IF('實驗一 特性曲線'!R10="","",TEXT('實驗一 特性曲線'!R10,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>IF('實驗一 特性曲線'!I9="","",TEXT('實驗一 特性曲線'!I9,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="B18" s="16">
+        <f>IF('實驗一 特性曲線'!M11="","",TEXT('實驗一 特性曲線'!M11,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="E18" s="15">
-        <f>IF('實驗一 特性曲線'!L9="","",TEXT('實驗一 特性曲線'!L9,"0.000")&amp;" mA")</f>
+      <c r="E18" s="16">
+        <f>IF('實驗一 特性曲線'!R11="","",TEXT('實驗一 特性曲線'!R11,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="B19" s="15">
-        <f>IF('實驗一 特性曲線'!I10="","",TEXT('實驗一 特性曲線'!I10,"0.000")&amp;" mA")</f>
-        <v/>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="B19" s="16">
+        <f>IF('實驗一 特性曲線'!M12="","",TEXT('實驗一 特性曲線'!M12,"0.000")&amp;" mA")</f>
+        <v/>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="E19" s="15">
-        <f>IF('實驗一 特性曲線'!L10="","",TEXT('實驗一 特性曲線'!L10,"0.000")&amp;" mA")</f>
+      <c r="E19" s="16">
+        <f>IF('實驗一 特性曲線'!R12="","",TEXT('實驗一 特性曲線'!R12,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
@@ -2767,260 +3081,260 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>V_DS = 1 V</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
+      <c r="B23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>V_GS (experimental setting)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>0.5 V</t>
         </is>
       </c>
-      <c r="B25" s="15">
-        <f>IF('實驗二 轉移曲線'!C6="","",TEXT('實驗二 轉移曲線'!C6,"0.000")&amp;" mA")</f>
+      <c r="B25" s="16">
+        <f>IF('實驗二 轉移曲線'!D8="","",TEXT('實驗二 轉移曲線'!D8,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f>IF('實驗二 轉移曲線'!C7="","",TEXT('實驗二 轉移曲線'!C7,"0.000")&amp;" mA")</f>
+      <c r="B26" s="16">
+        <f>IF('實驗二 轉移曲線'!D9="","",TEXT('實驗二 轉移曲線'!D9,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="B27" s="15">
-        <f>IF('實驗二 轉移曲線'!C8="","",TEXT('實驗二 轉移曲線'!C8,"0.000")&amp;" mA")</f>
+      <c r="B27" s="16">
+        <f>IF('實驗二 轉移曲線'!D10="","",TEXT('實驗二 轉移曲線'!D10,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="B28" s="15">
-        <f>IF('實驗二 轉移曲線'!C9="","",TEXT('實驗二 轉移曲線'!C9,"0.000")&amp;" mA")</f>
+      <c r="B28" s="16">
+        <f>IF('實驗二 轉移曲線'!D11="","",TEXT('實驗二 轉移曲線'!D11,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="B29" s="15">
-        <f>IF('實驗二 轉移曲線'!C10="","",TEXT('實驗二 轉移曲線'!C10,"0.000")&amp;" mA")</f>
+      <c r="B29" s="16">
+        <f>IF('實驗二 轉移曲線'!D12="","",TEXT('實驗二 轉移曲線'!D12,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="B30" s="15">
-        <f>IF('實驗二 轉移曲線'!C11="","",TEXT('實驗二 轉移曲線'!C11,"0.000")&amp;" mA")</f>
+      <c r="B30" s="16">
+        <f>IF('實驗二 轉移曲線'!D13="","",TEXT('實驗二 轉移曲線'!D13,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>V_DS = 3 V</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
+      <c r="B32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>V_GS (experimental setting)</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>0.5 V</t>
         </is>
       </c>
-      <c r="B34" s="15">
-        <f>IF('實驗二 轉移曲線'!F6="","",TEXT('實驗二 轉移曲線'!F6,"0.000")&amp;" mA")</f>
+      <c r="B34" s="16">
+        <f>IF('實驗二 轉移曲線'!H8="","",TEXT('實驗二 轉移曲線'!H8,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="B35" s="15">
-        <f>IF('實驗二 轉移曲線'!F7="","",TEXT('實驗二 轉移曲線'!F7,"0.000")&amp;" mA")</f>
+      <c r="B35" s="16">
+        <f>IF('實驗二 轉移曲線'!H9="","",TEXT('實驗二 轉移曲線'!H9,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="B36" s="15">
-        <f>IF('實驗二 轉移曲線'!F8="","",TEXT('實驗二 轉移曲線'!F8,"0.000")&amp;" mA")</f>
+      <c r="B36" s="16">
+        <f>IF('實驗二 轉移曲線'!H10="","",TEXT('實驗二 轉移曲線'!H10,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="B37" s="15">
-        <f>IF('實驗二 轉移曲線'!F9="","",TEXT('實驗二 轉移曲線'!F9,"0.000")&amp;" mA")</f>
+      <c r="B37" s="16">
+        <f>IF('實驗二 轉移曲線'!H11="","",TEXT('實驗二 轉移曲線'!H11,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="B38" s="15">
-        <f>IF('實驗二 轉移曲線'!F10="","",TEXT('實驗二 轉移曲線'!F10,"0.000")&amp;" mA")</f>
+      <c r="B38" s="16">
+        <f>IF('實驗二 轉移曲線'!H12="","",TEXT('實驗二 轉移曲線'!H12,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="B39" s="15">
-        <f>IF('實驗二 轉移曲線'!F11="","",TEXT('實驗二 轉移曲線'!F11,"0.000")&amp;" mA")</f>
+      <c r="B39" s="16">
+        <f>IF('實驗二 轉移曲線'!H13="","",TEXT('實驗二 轉移曲線'!H13,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>V_DS = 5 V</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
+      <c r="B41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>V_GS (experimental setting)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>I_D (measure)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>0.5 V</t>
         </is>
       </c>
-      <c r="B43" s="15">
-        <f>IF('實驗二 轉移曲線'!I6="","",TEXT('實驗二 轉移曲線'!I6,"0.000")&amp;" mA")</f>
+      <c r="B43" s="16">
+        <f>IF('實驗二 轉移曲線'!L8="","",TEXT('實驗二 轉移曲線'!L8,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>1 V</t>
         </is>
       </c>
-      <c r="B44" s="15">
-        <f>IF('實驗二 轉移曲線'!I7="","",TEXT('實驗二 轉移曲線'!I7,"0.000")&amp;" mA")</f>
+      <c r="B44" s="16">
+        <f>IF('實驗二 轉移曲線'!L9="","",TEXT('實驗二 轉移曲線'!L9,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>2 V</t>
         </is>
       </c>
-      <c r="B45" s="15">
-        <f>IF('實驗二 轉移曲線'!I8="","",TEXT('實驗二 轉移曲線'!I8,"0.000")&amp;" mA")</f>
+      <c r="B45" s="16">
+        <f>IF('實驗二 轉移曲線'!L10="","",TEXT('實驗二 轉移曲線'!L10,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>3 V</t>
         </is>
       </c>
-      <c r="B46" s="15">
-        <f>IF('實驗二 轉移曲線'!I9="","",TEXT('實驗二 轉移曲線'!I9,"0.000")&amp;" mA")</f>
+      <c r="B46" s="16">
+        <f>IF('實驗二 轉移曲線'!L11="","",TEXT('實驗二 轉移曲線'!L11,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>4 V</t>
         </is>
       </c>
-      <c r="B47" s="15">
-        <f>IF('實驗二 轉移曲線'!I10="","",TEXT('實驗二 轉移曲線'!I10,"0.000")&amp;" mA")</f>
+      <c r="B47" s="16">
+        <f>IF('實驗二 轉移曲線'!L12="","",TEXT('實驗二 轉移曲線'!L12,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>5 V</t>
         </is>
       </c>
-      <c r="B48" s="15">
-        <f>IF('實驗二 轉移曲線'!I11="","",TEXT('實驗二 轉移曲線'!I11,"0.000")&amp;" mA")</f>
+      <c r="B48" s="16">
+        <f>IF('實驗二 轉移曲線'!L13="","",TEXT('實驗二 轉移曲線'!L13,"0.000")&amp;" mA")</f>
         <v/>
       </c>
     </row>
